--- a/data/trans_orig/IP18_E_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP18_E_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91282</t>
+          <t>91477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98298</t>
+          <t>98327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89324</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100316</t>
+          <t>100002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>183478</t>
+          <t>183962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>196654</t>
+          <t>196465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9371</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17709</t>
+          <t>17733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24208</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204390</t>
+          <t>205108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>216565</t>
+          <t>217256</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>208515</t>
+          <t>208387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219747</t>
+          <t>220839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>417824</t>
+          <t>417551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>434555</t>
+          <t>434318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10933</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21033</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22491</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91851</t>
+          <t>91840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99836</t>
+          <t>99872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101151</t>
+          <t>101075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109645</t>
+          <t>109561</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>196438</t>
+          <t>196700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>208276</t>
+          <t>208321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19877</t>
+          <t>19615</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141624</t>
+          <t>141260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151529</t>
+          <t>151569</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147373</t>
+          <t>147326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158037</t>
+          <t>157767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292642</t>
+          <t>291990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>307499</t>
+          <t>306999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>541227</t>
+          <t>541509</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>559988</t>
+          <t>559492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>559770</t>
+          <t>559408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>579694</t>
+          <t>579792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1106523</t>
+          <t>1106063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1134395</t>
+          <t>1134911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>29489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>47472</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>53918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>67912</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95784</t>
+          <t>96244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>125614</t>
+          <t>124627</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>136061</t>
+          <t>135898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130527</t>
+          <t>129898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138806</t>
+          <t>138729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>259852</t>
+          <t>259643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>272292</t>
+          <t>272747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15884</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>10626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>206745</t>
+          <t>207125</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>217178</t>
+          <t>216916</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>236900</t>
+          <t>237092</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>248077</t>
+          <t>248351</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>448192</t>
+          <t>448418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>462959</t>
+          <t>463446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14964</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18926</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29343</t>
+          <t>29117</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>136886</t>
+          <t>137085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146905</t>
+          <t>146837</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>132210</t>
+          <t>133189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143364</t>
+          <t>143909</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274333</t>
+          <t>274141</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288662</t>
+          <t>288620</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>14080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26130</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138143</t>
+          <t>138571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147044</t>
+          <t>147082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150364</t>
+          <t>150487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160153</t>
+          <t>159875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292401</t>
+          <t>290942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304817</t>
+          <t>304409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,2%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11627</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>25502</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>619523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>639591</t>
+          <t>640023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>662339</t>
+          <t>661538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>682374</t>
+          <t>682051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1290435</t>
+          <t>1291657</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1318748</t>
+          <t>1317988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>46491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59066</t>
+          <t>59826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>87379</t>
+          <t>86157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113438</t>
+          <t>112766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122068</t>
+          <t>122169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101842</t>
+          <t>101858</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111012</t>
+          <t>110967</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218530</t>
+          <t>218265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231143</t>
+          <t>231054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13465</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178848</t>
+          <t>178578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188718</t>
+          <t>188502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>216785</t>
+          <t>216811</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>227428</t>
+          <t>227555</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>398927</t>
+          <t>399001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>413755</t>
+          <t>413955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30872</t>
+          <t>30798</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>153342</t>
+          <t>153634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164292</t>
+          <t>163858</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>154612</t>
+          <t>155285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164334</t>
+          <t>164679</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312392</t>
+          <t>312107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>326600</t>
+          <t>326304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17949</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14334</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28246</t>
+          <t>28531</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140560</t>
+          <t>139679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149698</t>
+          <t>149308</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132158</t>
+          <t>133232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>143462</t>
+          <t>143484</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276754</t>
+          <t>276664</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>290509</t>
+          <t>290604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>14131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16402</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25617</t>
+          <t>25707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>597946</t>
+          <t>597539</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>616934</t>
+          <t>616918</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>619551</t>
+          <t>619529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>638985</t>
+          <t>638715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1223471</t>
+          <t>1222887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1251004</t>
+          <t>1251511</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>49275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64869</t>
+          <t>64362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>92402</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15234</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28164</t>
+          <t>27705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33361</t>
+          <t>33310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5717</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6578</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21200</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26858</t>
+          <t>26793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48563</t>
+          <t>48574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57900</t>
+          <t>57673</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,13%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>8466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28170</t>
+          <t>28505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,7 +7295,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>34174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50007</t>
+          <t>50773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64779</t>
+          <t>64733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>17394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23830</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41679</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57467</t>
+          <t>57028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64676</t>
+          <t>64455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74582</t>
+          <t>73912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89702</t>
+          <t>89845</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117908</t>
+          <t>117893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>127257</t>
+          <t>127020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>195974</t>
+          <t>196061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>215015</t>
+          <t>215028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>26402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>13699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35932</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
